--- a/backend/models/tabpfn_smote/leaderboard.xlsx
+++ b/backend/models/tabpfn_smote/leaderboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,26 @@
           <t>fit_order</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,22 +533,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2616150379180908</v>
+        <v>0.2508206367492676</v>
       </c>
       <c r="F2" t="n">
-        <v>1.796586990356445</v>
+        <v>1.703394651412964</v>
       </c>
       <c r="G2" t="n">
-        <v>2.781962156295776</v>
+        <v>2.676723003387451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2616150379180908</v>
+        <v>0.2508206367492676</v>
       </c>
       <c r="I2" t="n">
-        <v>1.796586990356445</v>
+        <v>1.703394651412964</v>
       </c>
       <c r="J2" t="n">
-        <v>2.781962156295776</v>
+        <v>2.676723003387451</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -537,6 +557,18 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -558,22 +590,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2624835968017578</v>
+        <v>0.2516798973083496</v>
       </c>
       <c r="F3" t="n">
-        <v>1.79686427116394</v>
+        <v>1.703616142272949</v>
       </c>
       <c r="G3" t="n">
-        <v>2.783267974853516</v>
+        <v>2.67787504196167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008685588836669922</v>
+        <v>0.0008592605590820312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002772808074951172</v>
+        <v>0.0002214908599853516</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001305818557739258</v>
+        <v>0.00115203857421875</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -583,6 +615,18 @@
       </c>
       <c r="M3" t="n">
         <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -603,22 +647,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5197334289550781</v>
+        <v>0.5011963844299316</v>
       </c>
       <c r="F4" t="n">
-        <v>3.616210460662842</v>
+        <v>3.446619987487793</v>
       </c>
       <c r="G4" t="n">
-        <v>5.640917301177979</v>
+        <v>5.384406566619873</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2581183910369873</v>
+        <v>0.2503757476806641</v>
       </c>
       <c r="I4" t="n">
-        <v>1.819623470306396</v>
+        <v>1.743225336074829</v>
       </c>
       <c r="J4" t="n">
-        <v>2.858955144882202</v>
+        <v>2.707683563232422</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -628,6 +672,18 @@
       </c>
       <c r="M4" t="n">
         <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -648,22 +704,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5206279754638672</v>
+        <v>0.5020148754119873</v>
       </c>
       <c r="F5" t="n">
-        <v>3.616446971893311</v>
+        <v>3.446846723556519</v>
       </c>
       <c r="G5" t="n">
-        <v>5.642115116119385</v>
+        <v>5.385557174682617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0008945465087890625</v>
+        <v>0.0008184909820556641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00023651123046875</v>
+        <v>0.0002267360687255859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00119781494140625</v>
+        <v>0.001150608062744141</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -673,6 +729,18 @@
       </c>
       <c r="M5" t="n">
         <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
